--- a/liczby_zespolone/Rejestr_pracy.xlsx
+++ b/liczby_zespolone/Rejestr_pracy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\5c\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\5c\Desktop\Praca\project-tai\liczby_zespolone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A976B93A-C00E-4DD0-A0B8-5D4B33E1A9C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A35DF85-53E6-4A3E-8122-976AD2A3CBA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="4" xr2:uid="{27F76C89-BD38-4F29-8844-D7C5C0A2FD74}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5556" activeTab="6" xr2:uid="{27F76C89-BD38-4F29-8844-D7C5C0A2FD74}"/>
   </bookViews>
   <sheets>
     <sheet name="03.02.26" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="03.03.26" sheetId="4" r:id="rId3"/>
     <sheet name="10.03.26" sheetId="5" r:id="rId4"/>
     <sheet name="17.03.26" sheetId="6" r:id="rId5"/>
-    <sheet name="Podsumowanie " sheetId="7" r:id="rId6"/>
+    <sheet name="24.03.2026" sheetId="9" r:id="rId6"/>
+    <sheet name="Podsumowanie " sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="52">
   <si>
     <t>Rejestracja Czasu Pracy</t>
   </si>
@@ -395,6 +396,42 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -405,42 +442,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -796,54 +797,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="J2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="J2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="J3" s="14" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="J3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
@@ -864,14 +865,14 @@
       <c r="G5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -896,14 +897,14 @@
       <c r="J6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="23">
         <f>SUM(G6:G15)</f>
         <v>0.12500000000000006</v>
       </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -967,12 +968,12 @@
         <f t="shared" si="0"/>
         <v>1.041666666666663E-2</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="19"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="18"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -994,12 +995,12 @@
         <f t="shared" si="0"/>
         <v>1.0416666666666685E-2</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="25"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="15"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
@@ -1013,12 +1014,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="25"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="15"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
@@ -1032,12 +1033,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="25"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="15"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
@@ -1068,12 +1069,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="28" t="s">
+      <c r="J14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="19"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="18"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
@@ -1087,28 +1088,28 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="23" t="s">
+      <c r="J15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="25"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="J16" s="23" t="s">
+      <c r="J16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="25"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="15"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="J17" s="23" t="s">
+      <c r="J17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="25"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="20" spans="3:13" ht="16.8" x14ac:dyDescent="0.3">
       <c r="C20" s="7"/>
@@ -1116,21 +1117,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="B3:G4"/>
+    <mergeCell ref="J3:O4"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="K6:O6"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="J10:M10"/>
     <mergeCell ref="J11:M11"/>
     <mergeCell ref="J12:M12"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="B3:G4"/>
-    <mergeCell ref="J3:O4"/>
-    <mergeCell ref="J5:O5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1151,54 +1152,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="J2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="J2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="J3" s="14" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="J3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
@@ -1219,14 +1220,14 @@
       <c r="G5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -1251,14 +1252,14 @@
       <c r="J6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="23">
         <f>SUM(G6:G15)</f>
         <v>0.12152777777777785</v>
       </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -1451,54 +1452,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="J2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="J2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="J3" s="14" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="J3" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
@@ -1519,14 +1520,14 @@
       <c r="G5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -1551,14 +1552,14 @@
       <c r="J6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="23">
         <f>SUM(G6:G15)</f>
         <v>0.13541666666666669</v>
       </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -1718,54 +1719,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="J2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="J2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="J3" s="14" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="J3" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
@@ -1786,14 +1787,14 @@
       <c r="G5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -1818,14 +1819,14 @@
       <c r="J6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="23">
         <f>SUM(G6:G15)</f>
         <v>0.13541666666666669</v>
       </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -1983,7 +1984,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A763C5-2009-48CD-BCA6-B2B22DB1D585}">
-  <dimension ref="B2:O15"/>
+  <dimension ref="B2:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="31.77734375" customWidth="1"/>
@@ -1991,54 +1992,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="J2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="J2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="J3" s="14" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="J3" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
@@ -2059,14 +2060,14 @@
       <c r="G5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -2082,23 +2083,23 @@
         <v>0.30555555555555552</v>
       </c>
       <c r="F6" s="5">
-        <v>0.31944444444444448</v>
+        <v>0.32291666666666669</v>
       </c>
       <c r="G6" s="5">
         <f>F6-E6</f>
-        <v>1.3888888888888951E-2</v>
+        <v>1.736111111111116E-2</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="26">
-        <f>SUM(G6:G15)</f>
-        <v>8.680555555555558E-2</v>
-      </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
+      <c r="K6" s="23">
+        <f>SUM(G6:G14)</f>
+        <v>9.7222222222222265E-2</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -2111,14 +2112,14 @@
         <v>14</v>
       </c>
       <c r="E7" s="5">
-        <v>0.32291666666666669</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="F7" s="5">
-        <v>0.33680555555555558</v>
+        <v>0.34375</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" ref="G7:G15" si="0">F7-E7</f>
-        <v>1.3888888888888895E-2</v>
+        <f t="shared" ref="G7:G14" si="0">F7-E7</f>
+        <v>1.7361111111111105E-2</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
@@ -2132,14 +2133,14 @@
         <v>45</v>
       </c>
       <c r="E8" s="5">
-        <v>0.34027777777777773</v>
+        <v>0.34375</v>
       </c>
       <c r="F8" s="5">
         <v>0.375</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>3.4722222222222265E-2</v>
+        <v>3.125E-2</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
@@ -2153,58 +2154,58 @@
         <v>50</v>
       </c>
       <c r="E9" s="5">
-        <v>0.37847222222222227</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="F9" s="5">
-        <v>0.39583333333333331</v>
+        <v>0.40625</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>1.7361111111111049E-2</v>
+        <v>2.430555555555558E-2</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.4375</v>
+      </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.9444444444444198E-3</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.4375</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>6.9444444444444198E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2212,7 +2213,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -2225,26 +2226,13 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="2">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2264,6 +2252,248 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EF4CAAA-1F5C-4F7B-B75F-63B05F782549}">
+  <dimension ref="B2:O15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="31.77734375" customWidth="1"/>
+    <col min="4" max="4" width="69.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="J2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="J3" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f>F6-E6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="23">
+        <f>SUM(G6:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5">
+        <f t="shared" ref="G7:G15" si="0">F7-E7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="B3:G4"/>
+    <mergeCell ref="J3:O4"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="K6:O6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8217A4CA-ED8E-494A-84C1-89B87B7F7028}">
   <dimension ref="B2:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2272,42 +2502,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
@@ -2373,7 +2603,9 @@
       <c r="B11" s="10">
         <v>5</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="34">
+        <v>9.7222222222222224E-2</v>
+      </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
@@ -2393,14 +2625,14 @@
       <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="23">
         <f>SUM(C7:G12)</f>
-        <v>0.51736111111111105</v>
-      </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+        <v>0.61458333333333326</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="11">
